--- a/salidas/empresas/FISV.xlsx
+++ b/salidas/empresas/FISV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1399,7 +1411,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1424,7 +1436,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,7 +1486,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1674,7 +1686,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1724,7 +1736,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1749,7 +1761,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1807,7 +1819,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1836,7 +1848,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1865,7 +1877,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1894,7 +1906,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1923,7 +1935,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1952,7 +1964,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1981,7 +1993,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2010,7 +2022,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2039,7 +2051,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2097,7 +2109,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2126,7 +2138,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2155,7 +2167,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2184,7 +2196,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2213,7 +2225,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2242,7 +2254,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2300,7 +2312,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2329,7 +2341,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2358,7 +2370,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2387,7 +2399,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2416,7 +2428,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2445,7 +2457,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2474,7 +2486,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2503,7 +2515,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2561,7 +2573,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2590,7 +2602,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2619,7 +2631,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2648,7 +2660,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2677,7 +2689,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2706,7 +2718,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2735,7 +2747,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2764,7 +2776,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2793,7 +2805,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2822,7 +2834,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,7 +2892,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2909,7 +2921,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2938,7 +2950,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2967,7 +2979,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2996,7 +3008,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3025,7 +3037,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3083,7 +3095,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3112,7 +3124,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3141,7 +3153,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3170,7 +3182,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3199,7 +3211,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3228,7 +3240,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3286,7 +3298,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3315,7 +3327,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3344,7 +3356,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3373,7 +3385,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3402,7 +3414,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3431,7 +3443,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3460,7 +3472,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3489,7 +3501,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3518,7 +3530,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3547,7 +3559,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3576,7 +3588,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3605,7 +3617,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3634,7 +3646,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3663,7 +3675,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3692,7 +3704,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3721,7 +3733,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3750,7 +3762,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3779,7 +3791,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3808,7 +3820,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3837,7 +3849,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3895,7 +3907,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3924,7 +3936,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3953,7 +3965,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3982,7 +3994,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4011,7 +4023,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4040,7 +4052,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4069,7 +4081,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4098,7 +4110,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4127,7 +4139,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4156,7 +4168,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4185,7 +4197,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4214,7 +4226,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4243,7 +4255,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4272,7 +4284,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4301,7 +4313,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4330,7 +4342,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4359,7 +4371,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4388,7 +4400,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4417,7 +4429,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4446,7 +4458,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4475,7 +4487,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4504,7 +4516,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4533,7 +4545,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4562,7 +4574,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4591,7 +4603,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4620,7 +4632,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4649,7 +4661,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4678,7 +4690,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4707,7 +4719,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4736,7 +4748,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4765,7 +4777,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4794,7 +4806,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4823,7 +4835,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4852,7 +4864,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4881,7 +4893,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4910,7 +4922,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4939,7 +4951,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4968,7 +4980,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5026,7 +5038,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5055,7 +5067,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5084,7 +5096,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5113,7 +5125,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5142,7 +5154,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5171,7 +5183,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5200,7 +5212,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5229,7 +5241,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5258,7 +5270,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5287,7 +5299,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5316,7 +5328,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5345,7 +5357,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5374,7 +5386,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5403,7 +5415,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5432,7 +5444,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5461,7 +5473,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5490,7 +5502,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5519,7 +5531,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5548,7 +5560,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5577,7 +5589,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5606,7 +5618,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5635,7 +5647,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5664,7 +5676,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5693,7 +5705,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5722,7 +5734,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5751,7 +5763,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5780,7 +5792,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5838,7 +5850,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5867,7 +5879,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5896,7 +5908,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5925,7 +5937,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5954,7 +5966,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5983,7 +5995,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6012,7 +6024,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6041,7 +6053,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6070,7 +6082,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6099,7 +6111,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6128,7 +6140,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6157,7 +6169,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6186,7 +6198,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6215,7 +6227,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6244,7 +6256,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6273,7 +6285,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6302,7 +6314,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6331,7 +6343,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6360,7 +6372,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6389,7 +6401,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6418,7 +6430,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6447,7 +6459,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6476,7 +6488,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6505,7 +6517,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6534,7 +6546,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6563,7 +6575,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6592,7 +6604,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6621,7 +6633,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6650,7 +6662,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6679,7 +6691,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6708,7 +6720,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6737,7 +6749,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6766,7 +6778,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6795,7 +6807,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6824,7 +6836,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6853,7 +6865,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6882,7 +6894,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6911,7 +6923,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6969,7 +6981,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6998,7 +7010,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7027,7 +7039,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7056,7 +7068,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7085,7 +7097,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7114,7 +7126,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7143,7 +7155,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7172,32 +7184,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>45.95000076293945</v>
+        <v>45.97999954223633</v>
       </c>
       <c r="C250" t="n">
-        <v>45.95000076293945</v>
+        <v>45.97999954223633</v>
       </c>
       <c r="D250" t="n">
-        <v>119137300</v>
+        <v>127291300</v>
       </c>
       <c r="E250" t="n">
         <v>5.21</v>
       </c>
       <c r="F250" t="n">
-        <v>8.819577881562275</v>
+        <v>8.825335804651887</v>
       </c>
       <c r="G250" t="n">
         <v>531766721</v>
       </c>
       <c r="H250" t="n">
-        <v>24434681235.65581</v>
+        <v>24450633588.15651</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2240405337437429</v>
+        <v>0.239374325193998</v>
       </c>
     </row>
   </sheetData>
@@ -7229,75 +7241,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7534,7 +7546,7 @@
       <c r="I7" t="n">
         <v>0.7648326898326898</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K7" t="n">
@@ -7547,13 +7559,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7580,7 +7592,7 @@
       <c r="I8" t="n">
         <v>0.7973326898326898</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K8" t="n">
@@ -7593,13 +7605,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7626,7 +7638,7 @@
       <c r="I9" t="n">
         <v>0.7798326898326898</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K9" t="n">
@@ -7639,13 +7651,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7672,7 +7684,7 @@
       <c r="I10" t="n">
         <v>0.8123326898326899</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K10" t="n">
@@ -7685,13 +7697,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7718,7 +7730,7 @@
       <c r="I11" t="n">
         <v>0.8174999999999999</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K11" t="n">
@@ -7731,13 +7743,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7764,7 +7776,7 @@
       <c r="I12" t="n">
         <v>0.8099999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="K12" t="n">
@@ -7777,13 +7789,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7810,7 +7822,7 @@
       <c r="I13" t="n">
         <v>0.7575</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="K13" t="n">
@@ -7823,13 +7835,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7856,7 +7868,7 @@
       <c r="I14" t="n">
         <v>0.7625</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="K14" t="n">
@@ -7869,13 +7881,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7902,7 +7914,7 @@
       <c r="I15" t="n">
         <v>0.8199999999999998</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7915,13 +7927,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7948,7 +7960,7 @@
       <c r="I16" t="n">
         <v>0.865</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K16" t="n">
@@ -7961,13 +7973,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7994,7 +8006,7 @@
       <c r="I17" t="n">
         <v>1.0025</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="K17" t="n">
@@ -8007,13 +8019,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8040,7 +8052,7 @@
       <c r="I18" t="n">
         <v>1.035</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="K18" t="n">
@@ -8053,13 +8065,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8086,7 +8098,7 @@
       <c r="I19" t="n">
         <v>1.11</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K19" t="n">
@@ -8099,13 +8111,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8132,7 +8144,7 @@
       <c r="I20" t="n">
         <v>1.09</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K20" t="n">
@@ -8145,13 +8157,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8178,7 +8190,7 @@
       <c r="I21" t="n">
         <v>1.08</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K21" t="n">
@@ -8191,13 +8203,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8224,7 +8236,7 @@
       <c r="I22" t="n">
         <v>1.1275</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K22" t="n">
@@ -8237,13 +8249,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8270,7 +8282,7 @@
       <c r="I23" t="n">
         <v>1.22</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="K23" t="n">
@@ -8283,13 +8295,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8316,7 +8328,7 @@
       <c r="I24" t="n">
         <v>1.33</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="K24" t="n">
@@ -8329,13 +8341,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8362,7 +8374,7 @@
       <c r="I25" t="n">
         <v>1.3725</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="K25" t="n">
@@ -8375,13 +8387,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8408,7 +8420,7 @@
       <c r="I26" t="n">
         <v>1.545</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K26" t="n">
@@ -8421,13 +8433,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8454,7 +8466,7 @@
       <c r="I27" t="n">
         <v>1.49</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K27" t="n">
@@ -8467,13 +8479,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8500,7 +8512,7 @@
       <c r="I28" t="n">
         <v>1.53</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K28" t="n">
@@ -8513,13 +8525,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8546,7 +8558,7 @@
       <c r="I29" t="n">
         <v>1.47</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K29" t="n">
@@ -8559,13 +8571,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8592,7 +8604,7 @@
       <c r="I30" t="n">
         <v>1.455</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="K30" t="n">
@@ -8605,13 +8617,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8638,7 +8650,7 @@
       <c r="I31" t="n">
         <v>1.495</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K31" t="n">
@@ -8651,13 +8663,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8684,7 +8696,7 @@
       <c r="I32" t="n">
         <v>1.765</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K32" t="n">
@@ -8697,13 +8709,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8730,7 +8742,7 @@
       <c r="I33" t="n">
         <v>1.97</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K33" t="n">
@@ -8743,13 +8755,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8776,7 +8788,7 @@
       <c r="I34" t="n">
         <v>1.99</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K34" t="n">
@@ -8789,13 +8801,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8822,7 +8834,7 @@
       <c r="I35" t="n">
         <v>2.075</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K35" t="n">
@@ -8835,13 +8847,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8868,7 +8880,7 @@
       <c r="I36" t="n">
         <v>2.005</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8881,13 +8893,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8914,7 +8926,7 @@
       <c r="I37" t="n">
         <v>2.045</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K37" t="n">
@@ -8927,13 +8939,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8960,7 +8972,7 @@
       <c r="I38" t="n">
         <v>2.105</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K38" t="n">
@@ -8973,13 +8985,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9006,7 +9018,7 @@
       <c r="I39" t="n">
         <v>2.89</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K39" t="n">
@@ -9019,13 +9031,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9052,7 +9064,7 @@
       <c r="I40" t="n">
         <v>3.325</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K40" t="n">
@@ -9065,13 +9077,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9098,7 +9110,7 @@
       <c r="I41" t="n">
         <v>3.415</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K41" t="n">
@@ -9111,13 +9123,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9144,7 +9156,7 @@
       <c r="I42" t="n">
         <v>3.425</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="K42" t="n">
@@ -9157,13 +9169,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9190,7 +9202,7 @@
       <c r="I43" t="n">
         <v>2.87</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K43" t="n">
@@ -9203,13 +9215,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9236,7 +9248,7 @@
       <c r="I44" t="n">
         <v>2.43</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K44" t="n">
@@ -9249,13 +9261,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9282,7 +9294,7 @@
       <c r="I45" t="n">
         <v>2.39</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K45" t="n">
@@ -9295,13 +9307,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9328,7 +9340,7 @@
       <c r="I46" t="n">
         <v>2.17</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="K46" t="n">
@@ -9341,13 +9353,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9374,7 +9386,7 @@
       <c r="I47" t="n">
         <v>1.71</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K47" t="n">
@@ -9387,13 +9399,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9420,7 +9432,7 @@
       <c r="I48" t="n">
         <v>1.72</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="K48" t="n">
@@ -9433,13 +9445,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9466,7 +9478,7 @@
       <c r="I49" t="n">
         <v>1.16</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K49" t="n">
@@ -9479,13 +9491,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9512,7 +9524,7 @@
       <c r="I50" t="n">
         <v>1.22</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K50" t="n">
@@ -9525,13 +9537,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9558,7 +9570,7 @@
       <c r="I51" t="n">
         <v>1.4</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K51" t="n">
@@ -9571,13 +9583,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9604,7 +9616,7 @@
       <c r="I52" t="n">
         <v>1.28</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K52" t="n">
@@ -9617,13 +9629,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9650,7 +9662,7 @@
       <c r="I53" t="n">
         <v>1.68</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K53" t="n">
@@ -9663,13 +9675,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9696,7 +9708,7 @@
       <c r="I54" t="n">
         <v>1.93</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9709,13 +9721,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9742,7 +9754,7 @@
       <c r="I55" t="n">
         <v>1.99</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K55" t="n">
@@ -9755,13 +9767,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9788,7 +9800,7 @@
       <c r="I56" t="n">
         <v>2.56</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9801,13 +9813,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9834,7 +9846,7 @@
       <c r="I57" t="n">
         <v>3.08</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K57" t="n">
@@ -9847,13 +9859,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9880,7 +9892,7 @@
       <c r="I58" t="n">
         <v>3.19</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K58" t="n">
@@ -9893,13 +9905,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9926,7 +9938,7 @@
       <c r="I59" t="n">
         <v>3.910000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9939,13 +9951,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9972,7 +9984,7 @@
       <c r="I60" t="n">
         <v>3.780000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K60" t="n">
@@ -9985,13 +9997,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10018,7 +10030,7 @@
       <c r="I61" t="n">
         <v>3.96</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -10031,13 +10043,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10064,7 +10076,7 @@
       <c r="I62" t="n">
         <v>4.77</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="K62" t="n">
@@ -10077,13 +10089,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10110,7 +10122,7 @@
       <c r="I63" t="n">
         <v>4.98</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K63" t="n">
@@ -10123,13 +10135,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10156,7 +10168,7 @@
       <c r="I64" t="n">
         <v>5.330000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="K64" t="n">
@@ -10169,13 +10181,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10202,7 +10214,7 @@
       <c r="I65" t="n">
         <v>5.76</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K65" t="n">
@@ -10215,13 +10227,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10248,7 +10260,7 @@
       <c r="I66" t="n">
         <v>5.18</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="K66" t="n">
@@ -10261,13 +10273,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10294,7 +10306,7 @@
       <c r="I67" t="n">
         <v>5.38</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="K67" t="n">
@@ -10307,13 +10319,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10340,7 +10352,7 @@
       <c r="I68" t="n">
         <v>5.649999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K68" t="n">
@@ -10353,13 +10365,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10386,7 +10398,7 @@
       <c r="I69" t="n">
         <v>5.98</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K69" t="n">
@@ -10399,13 +10411,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10432,7 +10444,7 @@
       <c r="I70" t="n">
         <v>6.46</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K70" t="n">
@@ -10445,13 +10457,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10478,7 +10490,7 @@
       <c r="I71" t="n">
         <v>6.34</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K71" t="n">
@@ -10491,13 +10503,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10524,7 +10536,7 @@
       <c r="I72" t="n">
         <v>5.9</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K72" t="n">
@@ -10537,13 +10549,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10570,7 +10582,7 @@
       <c r="I73" t="n">
         <v>5.21</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="K73" t="n">
@@ -10607,52 +10619,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40029</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="C2" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40120</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40233</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40302</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="C5" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40392</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C6" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40484</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40592</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="C8" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="C9" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="C10" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="C11" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40956</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C13" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41116</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="C14" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41207</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="C15" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C16" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41389</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C17" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41480</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C18" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41571</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C19" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="C20" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41753</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="C21" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41844</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="C22" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41935</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C23" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C24" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C25" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42208</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C26" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42299</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="C27" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C28" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C29" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C31" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42782</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C33" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42944</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C34" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43034</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C35" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43147</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C36" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43216</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43305</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="C38" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C39" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43511</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C40" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43580</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43668</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="C43" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43882</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C44" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="C45" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C46" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C47" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44246</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C48" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44309</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C49" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C50" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44491</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C51" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C52" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C53" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44764</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C54" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44855</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C55" t="n">
@@ -12377,10 +12389,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C56" t="n">
@@ -12409,10 +12421,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C57" t="n">
@@ -12441,10 +12453,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C58" t="n">
@@ -12473,10 +12485,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="C59" t="n">
@@ -12505,10 +12517,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C60" t="n">
@@ -12537,10 +12549,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="C61" t="n">
@@ -12569,10 +12581,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C62" t="n">
@@ -12601,10 +12613,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45583</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="C63" t="n">
@@ -12633,10 +12645,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45702</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="C64" t="n">
@@ -12665,10 +12677,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45765</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C65" t="n">
@@ -12697,10 +12709,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C66" t="n">
@@ -12729,10 +12741,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C67" t="n">
@@ -12761,10 +12773,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C68" t="n">
@@ -12793,10 +12805,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C69" t="n">
@@ -12825,10 +12837,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="C70" t="n">
@@ -12875,12 +12887,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
